--- a/public/downloads/Gauthierrole2021.xlsx
+++ b/public/downloads/Gauthierrole2021.xlsx
@@ -1590,16 +1590,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6495403412971887</v>
+        <v>-0.5982303758049774</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5726223980988582</v>
+        <v>0.5660502965702845</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4648118718784444</v>
+        <v>0.4620231887509259</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -1649,16 +1649,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3236296144096321</v>
+        <v>-0.532737062457656</v>
       </c>
       <c r="O4" s="5">
         <v>26</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5865862065162971</v>
+        <v>0.5459767549618704</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4597933651760094</v>
+        <v>0.4159351574972285</v>
       </c>
       <c r="R4" s="5">
         <v>25</v>
@@ -1708,16 +1708,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4399799788576155</v>
+        <v>-0.2087234716102877</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>1.095771180441274</v>
+        <v>1.075347174609562</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6504018523930568</v>
+        <v>0.6241424163237121</v>
       </c>
       <c r="R5" s="5">
         <v>21</v>
@@ -1767,16 +1767,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.2505925269536286</v>
+        <v>-0.5572054367187995</v>
       </c>
       <c r="O6" s="5">
         <v>20</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9390680002880284</v>
+        <v>0.9525610925396401</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.761326313630876</v>
+        <v>0.7131099706164752</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -1826,22 +1826,22 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.5624518772710552</v>
+        <v>-0.7006107865106852</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.6491410248470892</v>
+        <v>0.6101294220277689</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.7096967660718484</v>
+        <v>0.5526630217483272</v>
       </c>
       <c r="R7" s="5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -1885,16 +1885,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.043247088761904</v>
+        <v>-0.9214536210207491</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5156156715574153</v>
+        <v>0.5327146275326172</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3658890190486417</v>
+        <v>0.3480898044351927</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -1944,16 +1944,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.5092159116142199</v>
+        <v>-0.5876020176638121</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>0.7206723564097537</v>
+        <v>0.7260662008525701</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3683093967500939</v>
+        <v>0.3595998294112503</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -2003,16 +2003,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1584683863622573</v>
+        <v>-0.1731871970282839</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2393505368803756</v>
+        <v>0.2377655120716161</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.05781556345692877</v>
+        <v>0.05591353368641734</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -2062,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.6299137225462866</v>
+        <v>-0.6245140197735424</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>0.7634339291019571</v>
+        <v>0.7625339786398331</v>
       </c>
       <c r="Q11" s="4">
         <v>0.3468581522443751</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>-0.1586770275004938</v>
+        <v>-0.1808721980747805</v>
       </c>
       <c r="O12" s="5">
         <v>5</v>
       </c>
       <c r="P12" s="4">
-        <v>0.5019391619138616</v>
+        <v>0.5044052919776713</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.4138965344554481</v>
+        <v>0.4094575003405908</v>
       </c>
       <c r="R12" s="5">
         <v>5</v>
@@ -2180,16 +2180,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.5426196737300509</v>
+        <v>0.4330818447887737</v>
       </c>
       <c r="O13" s="5">
         <v>6</v>
       </c>
       <c r="P13" s="4">
-        <v>0.6524119271271009</v>
+        <v>0.6081503635302319</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6889363858146654</v>
+        <v>0.6555541997751977</v>
       </c>
       <c r="R13" s="5">
         <v>6</v>
@@ -2239,16 +2239,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.169123759356808</v>
+        <v>-1.037111865559638</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3424053451247382</v>
+        <v>0.3039125689386155</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3424053451247382</v>
+        <v>0.3039125689386155</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -2355,16 +2355,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.9619018298692573</v>
+        <v>-0.7070565556474264</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>1.222895485131999</v>
+        <v>1.101540907741608</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4031820779880922</v>
+        <v>0.3085256399639889</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -2537,13 +2537,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5427266793131442</v>
+        <v>-0.5448330349511679</v>
       </c>
       <c r="O3" s="5">
         <v>30</v>
       </c>
       <c r="P3" s="4">
-        <v>0.577006156444524</v>
+        <v>0.5768353708522519</v>
       </c>
       <c r="Q3" s="4">
         <v>0.5667733723235718</v>
@@ -2596,16 +2596,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9740260326976971</v>
+        <v>-1.000432349146706</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7115198910348409</v>
+        <v>0.7085858558738399</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3962029789882671</v>
+        <v>0.3949455353478381</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -2655,16 +2655,16 @@
         <v>2</v>
       </c>
       <c r="N5" s="4">
-        <v>0.03701521019482421</v>
+        <v>0.03743081605774989</v>
       </c>
       <c r="O5" s="5">
         <v>22</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9753272190172553</v>
+        <v>0.9753733974464693</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6976534921226923</v>
+        <v>0.6976950527089848</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -2714,22 +2714,22 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.020305308232204</v>
+        <v>-1.275000915318628</v>
       </c>
       <c r="O6" s="5">
         <v>17</v>
       </c>
       <c r="P6" s="4">
-        <v>0.701926559426354</v>
+        <v>0.7308976606555797</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6062787313075839</v>
+        <v>0.4774476963427734</v>
       </c>
       <c r="R6" s="5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -2773,16 +2773,16 @@
         <v>5</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.833376442454215</v>
+        <v>-2.042673495969836</v>
       </c>
       <c r="O7" s="5">
         <v>10</v>
       </c>
       <c r="P7" s="4">
-        <v>0.6089390050488226</v>
+        <v>0.5596199972167959</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.3350690422732169</v>
+        <v>0.2706460342957939</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -2832,16 +2832,16 @@
         <v>3</v>
       </c>
       <c r="N8" s="4">
-        <v>-2.145507243407857</v>
+        <v>-1.871770235520046</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5903792838553333</v>
+        <v>0.5447564492073648</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.5509315344443584</v>
+        <v>0.5118262476032426</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -2891,16 +2891,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4969946218126225</v>
+        <v>-0.3226823686797928</v>
       </c>
       <c r="O9" s="5">
         <v>10</v>
       </c>
       <c r="P9" s="4">
-        <v>0.6924993883958317</v>
+        <v>0.6142822618684853</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3685669099835908</v>
+        <v>0.3095688087773411</v>
       </c>
       <c r="R9" s="5">
         <v>10</v>
@@ -2950,16 +2950,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2109706642369941</v>
+        <v>-0.1051740983624256</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3657490720223864</v>
+        <v>0.3635780206331347</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.3584089499681742</v>
+        <v>0.3273991342773444</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -3009,16 +3009,16 @@
         <v>1</v>
       </c>
       <c r="N11" s="4">
-        <v>0.1473730447683463</v>
+        <v>0.02987227639829371</v>
       </c>
       <c r="O11" s="5">
         <v>11</v>
       </c>
       <c r="P11" s="4">
-        <v>0.682027662609205</v>
+        <v>0.6721771137272216</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.1863944124731798</v>
+        <v>0.1602047063671961</v>
       </c>
       <c r="R11" s="5">
         <v>9</v>
@@ -3182,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.795197288322953</v>
+        <v>-1.62367895407165</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
@@ -3298,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>-1.126294902275186</v>
+        <v>-1.093555797131955</v>
       </c>
       <c r="O16" s="5">
         <v>6</v>
@@ -3480,16 +3480,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1700381615087226</v>
+        <v>-0.2578032159907568</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4894731375978777</v>
+        <v>0.477650710272888</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4963646040058736</v>
+        <v>0.4866516941019129</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -3539,16 +3539,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1727552059379396</v>
+        <v>-0.1936740895230074</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.8086289862399954</v>
+        <v>0.7477754093622677</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.5863412649471187</v>
+        <v>0.5081009518186116</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -3598,22 +3598,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3443670834303612</v>
+        <v>-0.07098048211317298</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6063562416027412</v>
+        <v>0.5901053768126842</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.586040905945208</v>
+        <v>0.6148932667638164</v>
       </c>
       <c r="R5" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>0.2403427268390182</v>
+        <v>0.0065402760168638</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7313977785639586</v>
+        <v>0.7521886813026238</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.628942992674412</v>
+        <v>0.6048893589744481</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2832101613661951</v>
+        <v>0.3538822442734499</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5576556396375374</v>
+        <v>0.5597531292237232</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4981290857921132</v>
+        <v>0.4902766321357517</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -3775,13 +3775,13 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.4101737065948766</v>
+        <v>-0.4082256656779419</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5889882907212881</v>
+        <v>0.5893129642074441</v>
       </c>
       <c r="Q8" s="4">
         <v>0.4484136076770406</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.09280602295970415</v>
+        <v>-0.06753052783281532</v>
       </c>
       <c r="O9" s="5">
         <v>12</v>
@@ -3893,16 +3893,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.03674506976668271</v>
+        <v>-0.07268026044039289</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2774932956550079</v>
+        <v>0.2680680628328105</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.08107184937334097</v>
+        <v>0.07249767124082337</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -3952,16 +3952,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.3176713189729602</v>
+        <v>-0.2493254052928648</v>
       </c>
       <c r="O11" s="5">
         <v>12</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3370016579740343</v>
+        <v>0.3314890622078059</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3370016579740343</v>
+        <v>0.3314890622078059</v>
       </c>
       <c r="R11" s="5">
         <v>12</v>
@@ -4068,16 +4068,16 @@
         <v>2</v>
       </c>
       <c r="N13" s="4">
-        <v>1.559489317241102</v>
+        <v>1.386916341178406</v>
       </c>
       <c r="O13" s="5">
         <v>7</v>
       </c>
       <c r="P13" s="4">
-        <v>0.6520258925161008</v>
+        <v>0.6273726102214299</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6520258925161008</v>
+        <v>0.6273726102214299</v>
       </c>
       <c r="R13" s="5">
         <v>7</v>
@@ -4127,7 +4127,7 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.459492428552414</v>
+        <v>-0.5154039445407728</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
@@ -4243,16 +4243,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.2077946771579803</v>
+        <v>-0.2724369675685985</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.4947005266410797</v>
+        <v>0.4731530965042069</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.5546318957468801</v>
+        <v>0.5417034376647564</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -4425,16 +4425,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1768960023430803</v>
+        <v>-0.0740941580248915</v>
       </c>
       <c r="O3" s="5">
         <v>33</v>
       </c>
       <c r="P3" s="4">
-        <v>0.8055556691721085</v>
+        <v>0.7886241959670638</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4455565091758157</v>
+        <v>0.4328031509955041</v>
       </c>
       <c r="R3" s="5">
         <v>33</v>
@@ -4484,16 +4484,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3465233971563038</v>
+        <v>-0.3803420870935099</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4548996839390027</v>
+        <v>0.4548728863299274</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.2469374520409499</v>
+        <v>0.2450184395197144</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -4543,22 +4543,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.261847116878359</v>
+        <v>-0.04032651139343102</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>2.043251380407186</v>
+        <v>2.014295332351615</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5827338117028282</v>
+        <v>0.6140115698181127</v>
       </c>
       <c r="R5" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -4602,16 +4602,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.4299143446807564</v>
+        <v>-0.04993282297243695</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8393657685849077</v>
+        <v>0.8389865054750179</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6926729102830537</v>
+        <v>0.5790322449076323</v>
       </c>
       <c r="R6" s="5">
         <v>18</v>
@@ -4661,13 +4661,13 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.2071603383355871</v>
+        <v>0.2951216334478914</v>
       </c>
       <c r="O7" s="5">
         <v>8</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5519292895751953</v>
+        <v>0.5639365158547953</v>
       </c>
       <c r="Q7" s="4">
         <v>0.4412031372802723</v>
@@ -4720,16 +4720,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.111457681686473</v>
+        <v>-0.9647820915991474</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4385601257412875</v>
+        <v>0.4196417087792999</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3374149507468958</v>
+        <v>0.2958931070100985</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -4779,16 +4779,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.07236778395470651</v>
+        <v>0.3029948692437472</v>
       </c>
       <c r="O9" s="5">
         <v>5</v>
       </c>
       <c r="P9" s="4">
-        <v>1.141777746697527</v>
+        <v>1.180215594245701</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.5143721916437494</v>
+        <v>0.4682467745859412</v>
       </c>
       <c r="R9" s="5">
         <v>5</v>
@@ -4838,16 +4838,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1603986088147817</v>
+        <v>-0.1720638872027394</v>
       </c>
       <c r="O10" s="5">
         <v>7</v>
       </c>
       <c r="P10" s="4">
-        <v>0.4365294545745382</v>
+        <v>0.4306968153805594</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1988550379226074</v>
+        <v>0.1971885695814706</v>
       </c>
       <c r="R10" s="5">
         <v>7</v>
@@ -4897,16 +4897,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1140080804073463</v>
+        <v>-0.04000822648863789</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>1.407231464481836</v>
+        <v>1.38066720062815</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2892574657938062</v>
+        <v>0.2721803199531238</v>
       </c>
       <c r="R11" s="5">
         <v>10</v>
@@ -5013,16 +5013,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>1.365853368567389</v>
+        <v>1.464743469653314</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.5435857114129451</v>
+        <v>0.5577128687109345</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6031479087406206</v>
+        <v>0.5833698885234355</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -5072,16 +5072,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.075543681908158</v>
+        <v>-0.8059352476776098</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4242118065573474</v>
+        <v>0.3361923335925212</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.4242118065573474</v>
+        <v>0.3361923335925212</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -5188,16 +5188,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.6550937075745822</v>
+        <v>-0.3904545089569069</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>1.210538402483391</v>
+        <v>1.116300399655344</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4269662245065365</v>
+        <v>0.3668084608364154</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -5370,16 +5370,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3402956816905582</v>
+        <v>-0.3805943675268537</v>
       </c>
       <c r="O3" s="5">
         <v>33</v>
       </c>
       <c r="P3" s="4">
-        <v>0.7991212290668226</v>
+        <v>0.8002103827380738</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5100752318802739</v>
+        <v>0.5075565640155055</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -5429,16 +5429,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2664903261349494</v>
+        <v>-0.3627068539550748</v>
       </c>
       <c r="O4" s="5">
         <v>20</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6056330220256325</v>
+        <v>0.5824552471378086</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3724093361822817</v>
+        <v>0.3570759009860183</v>
       </c>
       <c r="R4" s="5">
         <v>20</v>
@@ -5488,22 +5488,22 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.3713462174984779</v>
+        <v>-0.1394082660778793</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>1.047052943269554</v>
+        <v>1.02519122446436</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6415720481057483</v>
+        <v>0.6847058331755543</v>
       </c>
       <c r="R5" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -5547,16 +5547,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3357407541227233</v>
+        <v>-0.1067603756030451</v>
       </c>
       <c r="O6" s="5">
         <v>21</v>
       </c>
       <c r="P6" s="4">
-        <v>1.00653689142847</v>
+        <v>0.9714170184208389</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.7858574158007172</v>
+        <v>0.650185752743949</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -5606,16 +5606,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.3826818430598486</v>
+        <v>-0.4455476673254282</v>
       </c>
       <c r="O7" s="5">
         <v>11</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5885630480116052</v>
+        <v>0.5807048199784077</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5267547558055909</v>
+        <v>0.5210396808723565</v>
       </c>
       <c r="R7" s="5">
         <v>11</v>
@@ -5665,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.7235602981036933</v>
+        <v>-0.5650320140649399</v>
       </c>
       <c r="O8" s="5">
         <v>11</v>
@@ -5674,7 +5674,7 @@
         <v>0.4440761774229003</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3907465122894382</v>
+        <v>0.376334850104097</v>
       </c>
       <c r="R8" s="5">
         <v>11</v>
@@ -5724,16 +5724,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.1530696702592778</v>
+        <v>-0.05313192598417515</v>
       </c>
       <c r="O9" s="5">
         <v>10</v>
       </c>
       <c r="P9" s="4">
-        <v>2.733879974570563</v>
+        <v>2.697082946189019</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3171585403799625</v>
+        <v>0.2929896551771307</v>
       </c>
       <c r="R9" s="5">
         <v>10</v>
@@ -5783,16 +5783,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.0241980824487257</v>
+        <v>-0.06146173305451441</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2917456492537444</v>
+        <v>0.2783196317895928</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1043752405852041</v>
+        <v>0.09571674974937991</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -5842,16 +5842,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.09450520221825939</v>
+        <v>0.01218508348848957</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>3.483385627208234</v>
+        <v>3.448923552184497</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3084844105283753</v>
+        <v>0.2884679776412398</v>
       </c>
       <c r="R11" s="5">
         <v>10</v>
@@ -5901,16 +5901,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.6557497316248657</v>
+        <v>0.4145578767160174</v>
       </c>
       <c r="O12" s="5">
         <v>6</v>
       </c>
       <c r="P12" s="4">
-        <v>0.631216041161524</v>
+        <v>0.5580879987399894</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.5197373799435638</v>
+        <v>0.4502439587960699</v>
       </c>
       <c r="R12" s="5">
         <v>6</v>
@@ -5960,16 +5960,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>0.9802533450569703</v>
+        <v>0.9534383514306626</v>
       </c>
       <c r="O13" s="5">
         <v>6</v>
       </c>
       <c r="P13" s="4">
-        <v>0.7101438411662935</v>
+        <v>0.7011655114313596</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6893874203038181</v>
+        <v>0.6833818678841131</v>
       </c>
       <c r="R13" s="5">
         <v>6</v>
@@ -6019,16 +6019,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.8459659021382606</v>
+        <v>-0.6644450487853817</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4122212593771716</v>
+        <v>0.3399364564387971</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.4122212593771716</v>
+        <v>0.3399364564387971</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -6078,16 +6078,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.1894123081162064</v>
+        <v>-0.2480959714001187</v>
       </c>
       <c r="O15" s="5">
         <v>5</v>
       </c>
       <c r="P15" s="4">
-        <v>0.7077574699976372</v>
+        <v>0.7026835905881773</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1475393289195734</v>
+        <v>0.129713940971439</v>
       </c>
       <c r="R15" s="5">
         <v>5</v>
@@ -6317,16 +6317,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.5299292817327834</v>
+        <v>-0.4412234754687603</v>
       </c>
       <c r="O3" s="5">
         <v>32</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5558007969972477</v>
+        <v>0.5496648663281253</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.468368259789956</v>
+        <v>0.4640456463995339</v>
       </c>
       <c r="R3" s="5">
         <v>32</v>
@@ -6376,16 +6376,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3398745685415784</v>
+        <v>-0.5260829534558127</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5504609209443541</v>
+        <v>0.5218645088751396</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4313290474388183</v>
+        <v>0.3877694333123171</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -6435,16 +6435,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5559370961924317</v>
+        <v>-0.40322484563535</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>1.033373381951427</v>
+        <v>1.003730044796002</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6155187253463136</v>
+        <v>0.5922756190447416</v>
       </c>
       <c r="R5" s="5">
         <v>22</v>
@@ -6494,16 +6494,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3538138472284216</v>
+        <v>-0.5942612497253492</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>1.112909565209886</v>
+        <v>1.134322696952279</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.701692519030152</v>
+        <v>0.6769931727189583</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.6372478841781773</v>
+        <v>-0.5300923104388175</v>
       </c>
       <c r="O7" s="5">
         <v>11</v>
@@ -6562,7 +6562,7 @@
         <v>0.5637424533325195</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5158980940437731</v>
+        <v>0.5061566782492858</v>
       </c>
       <c r="R7" s="5">
         <v>11</v>
@@ -6612,16 +6612,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.181745911899412</v>
+        <v>-1.032381657663564</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5340433574898308</v>
+        <v>0.5185063048551513</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4386404540100131</v>
+        <v>0.3717690081909168</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -6671,16 +6671,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.7336314511888432</v>
+        <v>-0.6642139167083698</v>
       </c>
       <c r="O9" s="5">
         <v>10</v>
       </c>
       <c r="P9" s="4">
-        <v>0.7734487668694681</v>
+        <v>0.7570995518961586</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3221806209390638</v>
+        <v>0.3164450698671871</v>
       </c>
       <c r="R9" s="5">
         <v>10</v>
@@ -6730,16 +6730,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2196682104157565</v>
+        <v>-0.2840820187201132</v>
       </c>
       <c r="O10" s="5">
         <v>11</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2777594253212247</v>
+        <v>0.2670237906038319</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1351068424399469</v>
+        <v>0.1292510416850053</v>
       </c>
       <c r="R10" s="5">
         <v>11</v>
@@ -6789,13 +6789,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.8374800080501685</v>
+        <v>-0.8180977498040676</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>0.8340674979238254</v>
+        <v>0.8308371215494752</v>
       </c>
       <c r="Q11" s="4">
         <v>0.3038918983222644</v>
@@ -6905,16 +6905,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.5195807092656309</v>
+        <v>0.5977066501953061</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4599355038934139</v>
+        <v>0.4710963525976532</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.5598227134281205</v>
+        <v>0.5441975252421856</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -6964,16 +6964,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.207077304649857</v>
+        <v>-1.064802056765728</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3727493152039945</v>
+        <v>0.3015317728515659</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3727493152039945</v>
+        <v>0.3015317728515659</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -7080,16 +7080,16 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>-1.110080661309934</v>
+        <v>-0.8584024688568093</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>1.191503953223951</v>
+        <v>1.035897634921871</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4122895963937435</v>
+        <v>0.2758976529218728</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -7262,16 +7262,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0254084098108938</v>
+        <v>0.02738244762753084</v>
       </c>
       <c r="O3" s="5">
         <v>37</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4298590538229689</v>
+        <v>0.4237257286375769</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4298590538229689</v>
+        <v>0.4237257286375769</v>
       </c>
       <c r="R3" s="5">
         <v>37</v>
@@ -7321,16 +7321,16 @@
         <v>2</v>
       </c>
       <c r="N4" s="4">
-        <v>0.3660591789663655</v>
+        <v>0.1194064115404672</v>
       </c>
       <c r="O4" s="5">
         <v>27</v>
       </c>
       <c r="P4" s="4">
-        <v>0.506111160219795</v>
+        <v>0.4479747348417721</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4244822203886937</v>
+        <v>0.3546231337489817</v>
       </c>
       <c r="R4" s="5">
         <v>26</v>
@@ -7380,22 +7380,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2090341988522789</v>
+        <v>0.0263096181432978</v>
       </c>
       <c r="O5" s="5">
         <v>27</v>
       </c>
       <c r="P5" s="4">
-        <v>0.5811490832917223</v>
+        <v>0.5319749351778134</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5257561414569274</v>
+        <v>0.5319749351778134</v>
       </c>
       <c r="R5" s="5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -7439,16 +7439,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>0.9620920910346956</v>
+        <v>0.5109823789298673</v>
       </c>
       <c r="O6" s="5">
         <v>21</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8359634288382608</v>
+        <v>0.8198669277565642</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6955408199883306</v>
+        <v>0.6223792788566195</v>
       </c>
       <c r="R6" s="5">
         <v>20</v>
@@ -7498,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.777491983667104</v>
+        <v>0.6883824727673016</v>
       </c>
       <c r="O7" s="5">
         <v>13</v>
@@ -7507,7 +7507,7 @@
         <v>0.5225581881660122</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4707746674259836</v>
+        <v>0.4639200896644602</v>
       </c>
       <c r="R7" s="5">
         <v>13</v>
@@ -7557,16 +7557,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.008505253603536999</v>
+        <v>0.06431394411135649</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2746161981738239</v>
+        <v>0.2652975331503109</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2776495980415777</v>
+        <v>0.266467200013362</v>
       </c>
       <c r="R8" s="5">
         <v>10</v>
@@ -7616,16 +7616,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.07886972543337596</v>
+        <v>0.1305295141985994</v>
       </c>
       <c r="O9" s="5">
         <v>12</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2232091109740517</v>
+        <v>0.2158028523114245</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2232091109740517</v>
+        <v>0.2158028523114245</v>
       </c>
       <c r="R9" s="5">
         <v>12</v>
@@ -7675,16 +7675,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.09235091582996156</v>
+        <v>0.008554467431565627</v>
       </c>
       <c r="O10" s="5">
         <v>11</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2520775894928058</v>
+        <v>0.1779749901895187</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2157529108305375</v>
+        <v>0.1440869282507267</v>
       </c>
       <c r="R10" s="5">
         <v>11</v>
@@ -7734,16 +7734,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.04641091064577318</v>
+        <v>-0.01059975310184313</v>
       </c>
       <c r="O11" s="5">
         <v>12</v>
       </c>
       <c r="P11" s="4">
-        <v>0.225099013637882</v>
+        <v>0.2204328418908546</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.225099013637882</v>
+        <v>0.2204328418908546</v>
       </c>
       <c r="R11" s="5">
         <v>12</v>
@@ -7793,13 +7793,13 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>1.466674358468719</v>
+        <v>1.390183040611319</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
       </c>
       <c r="P12" s="4">
-        <v>0.5058212944814291</v>
+        <v>0.4973222591639402</v>
       </c>
       <c r="Q12" s="4">
         <v>0.5367773091567365</v>
@@ -7852,16 +7852,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>1.814535581396971</v>
+        <v>1.902426694331297</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.5085900908216362</v>
+        <v>0.5211459640979683</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.592097417407607</v>
+        <v>0.574519194820742</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -7911,16 +7911,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2310436890805674</v>
+        <v>-0.004648098475553475</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3956978890648608</v>
+        <v>0.2634947015777896</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3956978890648608</v>
+        <v>0.2634947015777896</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -8027,16 +8027,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.1291006742487987</v>
+        <v>0.125851022009897</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.4182385836059294</v>
+        <v>0.2551420659366102</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4546071032936487</v>
+        <v>0.3024593369056596</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -8209,16 +8209,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.6155651035271839</v>
+        <v>-0.543202461274074</v>
       </c>
       <c r="O3" s="5">
         <v>37</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4591920630742926</v>
+        <v>0.450735839150866</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4591920630742926</v>
+        <v>0.450735839150866</v>
       </c>
       <c r="R3" s="5">
         <v>37</v>
@@ -8268,16 +8268,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.08903588705229026</v>
+        <v>-0.1593367947669968</v>
       </c>
       <c r="O4" s="5">
         <v>22</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5857566992532606</v>
+        <v>0.5737650511970632</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4112590239797759</v>
+        <v>0.3997374971705657</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -8327,16 +8327,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.9025919483441937</v>
+        <v>-0.5166812228869411</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6149451294457688</v>
+        <v>0.59323348887412</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6417163176931905</v>
+        <v>0.588811047808884</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -8386,22 +8386,22 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1040636756835808</v>
+        <v>-0.398150130844158</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7428291358935245</v>
+        <v>0.7483365442841128</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6410777952872706</v>
+        <v>0.5065423695241188</v>
       </c>
       <c r="R6" s="5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -8445,16 +8445,16 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.478154101111438</v>
+        <v>-0.4898641260248127</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5601755746289855</v>
+        <v>0.5587118215148137</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4535629211970024</v>
+        <v>0.4535629211970023</v>
       </c>
       <c r="R7" s="5">
         <v>12</v>
@@ -8504,16 +8504,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.5502854134495583</v>
+        <v>-0.3788206365118612</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5034105815685921</v>
+        <v>0.5131833710266033</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3768668754934155</v>
+        <v>0.3327423357915313</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -8563,16 +8563,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.522391173822278</v>
+        <v>-1.511236437982959</v>
       </c>
       <c r="O9" s="5">
         <v>12</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2948635951147989</v>
+        <v>0.2947445354287671</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2948635951147989</v>
+        <v>0.2947445354287671</v>
       </c>
       <c r="R9" s="5">
         <v>12</v>
@@ -8622,16 +8622,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.2871362816471232</v>
+        <v>-0.2494919300913807</v>
       </c>
       <c r="O10" s="5">
         <v>11</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2481693696598433</v>
+        <v>0.2388677722312794</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2283136153874195</v>
+        <v>0.2147442044148278</v>
       </c>
       <c r="R10" s="5">
         <v>11</v>
@@ -8681,16 +8681,16 @@
         <v>1</v>
       </c>
       <c r="N11" s="4">
-        <v>-1.436129355042803</v>
+        <v>-1.398817426646907</v>
       </c>
       <c r="O11" s="5">
         <v>12</v>
       </c>
       <c r="P11" s="4">
-        <v>0.3007634414259626</v>
+        <v>0.2990051290326381</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3007634414259626</v>
+        <v>0.2990051290326381</v>
       </c>
       <c r="R11" s="5">
         <v>12</v>
@@ -8740,13 +8740,13 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.3978865970872256</v>
+        <v>0.3568593317948938</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
       </c>
       <c r="P12" s="4">
-        <v>0.518105110953561</v>
+        <v>0.5135465259210797</v>
       </c>
       <c r="Q12" s="4">
         <v>0.4780705868078527</v>
@@ -8799,16 +8799,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>0.659689342307054</v>
+        <v>0.716161672768834</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.504851855245839</v>
+        <v>0.5129193310260932</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6184375479751509</v>
+        <v>0.6071430818827949</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -8858,16 +8858,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.6569202791934264</v>
+        <v>-0.4413380237580924</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4728350604591418</v>
+        <v>0.3725739035575693</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.4728350604591418</v>
+        <v>0.3725739035575693</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -8974,16 +8974,16 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.7969523011218037</v>
+        <v>-0.487104720779552</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.4537828946127858</v>
+        <v>0.3441601811946515</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.5075359205658054</v>
+        <v>0.3880262543346689</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -9156,16 +9156,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.04574004309652471</v>
+        <v>0.004142473308144545</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4361693063560412</v>
+        <v>0.431586552307598</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4411635483919551</v>
+        <v>0.4350678701642587</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -9215,16 +9215,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2071112356254338</v>
+        <v>0.0530843599855686</v>
       </c>
       <c r="O4" s="5">
         <v>26</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3881177857533276</v>
+        <v>0.3561165011116686</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3939994791428545</v>
+        <v>0.3548432652595985</v>
       </c>
       <c r="R4" s="5">
         <v>26</v>
@@ -9274,22 +9274,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.189163313188084</v>
+        <v>0.0353922356321057</v>
       </c>
       <c r="O5" s="5">
         <v>26</v>
       </c>
       <c r="P5" s="4">
-        <v>0.582047895043728</v>
+        <v>0.5464266549608924</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.5403237104162667</v>
+        <v>0.5523410748906764</v>
       </c>
       <c r="R5" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -9333,16 +9333,16 @@
         <v>4</v>
       </c>
       <c r="N6" s="4">
-        <v>0.8930788218600236</v>
+        <v>0.45328022500874</v>
       </c>
       <c r="O6" s="5">
         <v>21</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8355598378288596</v>
+        <v>0.8196500834673676</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6943657990693713</v>
+        <v>0.6222231012762643</v>
       </c>
       <c r="R6" s="5">
         <v>20</v>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>0.7592178883841765</v>
+        <v>0.8094861292489277</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
@@ -9451,16 +9451,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.0336347593759676</v>
+        <v>0.02407985521367983</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>0.2823191894964869</v>
+        <v>0.2734672537205644</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.2872252272234235</v>
+        <v>0.2766029042923165</v>
       </c>
       <c r="R8" s="5">
         <v>10</v>
@@ -9510,16 +9510,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>0.1658524760776577</v>
+        <v>0.1960451068928961</v>
       </c>
       <c r="O9" s="5">
         <v>12</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2203231990320719</v>
+        <v>0.2171330697499698</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2203231990320719</v>
+        <v>0.2171330697499698</v>
       </c>
       <c r="R9" s="5">
         <v>12</v>
@@ -9569,16 +9569,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.01903824112774781</v>
+        <v>0.01292611458207205</v>
       </c>
       <c r="O10" s="5">
         <v>12</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2062188174426249</v>
+        <v>0.187342212776791</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2062188174426249</v>
+        <v>0.187342212776791</v>
       </c>
       <c r="R10" s="5">
         <v>12</v>
@@ -9628,16 +9628,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.02711745738025917</v>
+        <v>0.05192224846270221</v>
       </c>
       <c r="O11" s="5">
         <v>12</v>
       </c>
       <c r="P11" s="4">
-        <v>0.2232827831222572</v>
+        <v>0.2180596668161978</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.2232827831222572</v>
+        <v>0.2180596668161978</v>
       </c>
       <c r="R11" s="5">
         <v>12</v>
@@ -9687,16 +9687,16 @@
         <v>2</v>
       </c>
       <c r="N12" s="4">
-        <v>1.427037262242504</v>
+        <v>1.339888768009672</v>
       </c>
       <c r="O12" s="5">
         <v>8</v>
       </c>
       <c r="P12" s="4">
-        <v>0.4981264325309102</v>
+        <v>0.4855849216210117</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.5381761752267513</v>
+        <v>0.5349605372322195</v>
       </c>
       <c r="R12" s="5">
         <v>8</v>
@@ -9746,16 +9746,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>1.745218192862409</v>
+        <v>1.827463720736688</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4979146537118471</v>
+        <v>0.5096640148367442</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.5929785266453098</v>
+        <v>0.5765294210704539</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -9805,16 +9805,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2831717482492335</v>
+        <v>-0.04309106034717747</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3893680951679365</v>
+        <v>0.261752872560001</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3893680951679365</v>
+        <v>0.261752872560001</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -9921,16 +9921,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.1449880360137065</v>
+        <v>0.1319842952538011</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>0.4115583488359492</v>
+        <v>0.2593808080298554</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4499961249287042</v>
+        <v>0.2997363970567598</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -10103,16 +10103,16 @@
         <v>2</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8212995567598395</v>
+        <v>-0.8348121141982432</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5084853488472585</v>
+        <v>0.5081201445921665</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.5133547306773838</v>
+        <v>0.5129686576077152</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -10162,16 +10162,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>0.165283460236846</v>
+        <v>-0.02207314715898256</v>
       </c>
       <c r="O4" s="5">
         <v>24</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5476192086750651</v>
+        <v>0.515088492410681</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4396860787840371</v>
+        <v>0.4008431091274148</v>
       </c>
       <c r="R4" s="5">
         <v>23</v>
@@ -10221,16 +10221,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.5104180193049523</v>
+        <v>-0.3449137841380292</v>
       </c>
       <c r="O5" s="5">
         <v>25</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6918574273070817</v>
+        <v>0.6689154797922149</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6232284556549306</v>
+        <v>0.5984511523388744</v>
       </c>
       <c r="R5" s="5">
         <v>25</v>
@@ -10280,16 +10280,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.005732938386973174</v>
+        <v>-0.2852746424875363</v>
       </c>
       <c r="O6" s="5">
         <v>20</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7476256078755851</v>
+        <v>0.7449095464727498</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6604674181341086</v>
+        <v>0.6154126919057635</v>
       </c>
       <c r="R6" s="5">
         <v>20</v>
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.2798296711525503</v>
+        <v>-0.4882118844587353</v>
       </c>
       <c r="O7" s="5">
         <v>13</v>
@@ -10348,13 +10348,13 @@
         <v>0.6147988309222234</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.6670842683962188</v>
+        <v>0.5245658874810992</v>
       </c>
       <c r="R7" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -10398,16 +10398,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>0.009504803015352318</v>
+        <v>0.1476432477251031</v>
       </c>
       <c r="O8" s="5">
         <v>9</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5053612758166783</v>
+        <v>0.5062934631649781</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4106272160659835</v>
+        <v>0.3658239842937998</v>
       </c>
       <c r="R8" s="5">
         <v>9</v>
@@ -10457,16 +10457,16 @@
         <v>1</v>
       </c>
       <c r="N9" s="4">
-        <v>-1.120192041599719</v>
+        <v>-1.039843239295948</v>
       </c>
       <c r="O9" s="5">
         <v>9</v>
       </c>
       <c r="P9" s="4">
-        <v>1.005036005560575</v>
+        <v>0.9884797346941644</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.341920620075477</v>
+        <v>0.3287732369540145</v>
       </c>
       <c r="R9" s="5">
         <v>9</v>
@@ -10516,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.05836200258549049</v>
+        <v>-0.1214748383841027</v>
       </c>
       <c r="O10" s="5">
         <v>11</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2689311354754844</v>
+        <v>0.2490301421621931</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1283558789539454</v>
+        <v>0.1123832349575015</v>
       </c>
       <c r="R10" s="5">
         <v>11</v>
@@ -10575,22 +10575,22 @@
         <v>2</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.01988412347999519</v>
+        <v>-0.728106511527244</v>
       </c>
       <c r="O11" s="5">
         <v>11</v>
       </c>
       <c r="P11" s="4">
-        <v>1.470584721446561</v>
+        <v>1.152850251050483</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.6837955679318442</v>
+        <v>0.3018549920026821</v>
       </c>
       <c r="R11" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S11" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="25" customHeight="1">
@@ -10634,16 +10634,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.6651710471397744</v>
+        <v>0.7944840939553615</v>
       </c>
       <c r="O12" s="5">
         <v>6</v>
       </c>
       <c r="P12" s="4">
-        <v>0.580586112905507</v>
+        <v>0.6031013520386952</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.4682050477267615</v>
+        <v>0.4373213830187505</v>
       </c>
       <c r="R12" s="5">
         <v>6</v>
@@ -10693,16 +10693,16 @@
         <v>1</v>
       </c>
       <c r="N13" s="4">
-        <v>0.7561478071679361</v>
+        <v>0.8752418801167039</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.628974521706941</v>
+        <v>0.6459879606996221</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6303395286136617</v>
+        <v>0.6065207140239082</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -10752,16 +10752,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.2707262984201317</v>
+        <v>-0.06010879768459709</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3984378707095316</v>
+        <v>0.3281873900627481</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3984378707095316</v>
+        <v>0.3281873900627481</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -10811,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.4235000465109472</v>
+        <v>-0.4808571607416638</v>
       </c>
       <c r="O15" s="5">
         <v>5</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3899406095266759</v>
+        <v>0.3590805977926189</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.2040022796260525</v>
+        <v>0.1784416883913273</v>
       </c>
       <c r="R15" s="5">
         <v>5</v>
@@ -10870,7 +10870,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.5390596452456554</v>
+        <v>-0.4938233632648998</v>
       </c>
       <c r="O16" s="5">
         <v>6</v>
@@ -10998,13 +10998,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>87.17948717948718</v>
+        <v>87.46438746438746</v>
       </c>
       <c r="C3" s="3">
         <v>9.116809116809117</v>
       </c>
       <c r="D3" s="3">
-        <v>3.703703703703703</v>
+        <v>3.418803418803419</v>
       </c>
       <c r="E3" s="3">
         <v>2.279202279202279</v>
@@ -11013,16 +11013,16 @@
         <v>0.5698005698005698</v>
       </c>
       <c r="G3" s="3">
-        <v>0.8547008547008548</v>
+        <v>0.5698005698005698</v>
       </c>
       <c r="H3" s="4">
-        <v>0.6987558686922537</v>
+        <v>0.6959476715260877</v>
       </c>
       <c r="I3" s="4">
-        <v>0.365023707481819</v>
+        <v>0.3620776293481963</v>
       </c>
       <c r="J3" s="4">
-        <v>1.553884522184009</v>
+        <v>1.549035605731323</v>
       </c>
       <c r="K3" s="4">
         <v>80.51756885090209</v>
@@ -11066,13 +11066,13 @@
         <v>0.8547008547008548</v>
       </c>
       <c r="H4" s="4">
-        <v>0.4829550879903786</v>
+        <v>0.4767034465214378</v>
       </c>
       <c r="I4" s="4">
-        <v>0.3564065891825825</v>
+        <v>0.3454145488083997</v>
       </c>
       <c r="J4" s="4">
-        <v>0.4647504844679499</v>
+        <v>0.4621721453228527</v>
       </c>
       <c r="K4" s="4">
         <v>70.55197007577951</v>
@@ -11116,13 +11116,13 @@
         <v>0.5698005698005698</v>
       </c>
       <c r="H5" s="4">
-        <v>0.4328115956766739</v>
+        <v>0.4281893033312938</v>
       </c>
       <c r="I5" s="4">
-        <v>0.3588217046627782</v>
+        <v>0.3455336407696392</v>
       </c>
       <c r="J5" s="4">
-        <v>0.4517883910273826</v>
+        <v>0.4462315102642088</v>
       </c>
       <c r="K5" s="4">
         <v>77.59763164525043</v>
@@ -11148,13 +11148,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="3">
-        <v>85.47008547008546</v>
+        <v>84.9002849002849</v>
       </c>
       <c r="C6" s="3">
         <v>11.11111111111111</v>
       </c>
       <c r="D6" s="3">
-        <v>3.418803418803419</v>
+        <v>3.988603988603988</v>
       </c>
       <c r="E6" s="3">
         <v>1.70940170940171</v>
@@ -11163,16 +11163,16 @@
         <v>0.5698005698005698</v>
       </c>
       <c r="G6" s="3">
-        <v>1.13960113960114</v>
+        <v>1.70940170940171</v>
       </c>
       <c r="H6" s="4">
-        <v>0.4731825394307994</v>
+        <v>0.46817571394673</v>
       </c>
       <c r="I6" s="4">
-        <v>0.3787304305278736</v>
+        <v>0.3562992625772506</v>
       </c>
       <c r="J6" s="4">
-        <v>0.5143088053434129</v>
+        <v>0.5207958161937631</v>
       </c>
       <c r="K6" s="4">
         <v>80.75014051204538</v>
@@ -11198,13 +11198,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="3">
-        <v>88.88888888888889</v>
+        <v>89.17378917378917</v>
       </c>
       <c r="C7" s="3">
         <v>6.837606837606838</v>
       </c>
       <c r="D7" s="3">
-        <v>4.273504273504273</v>
+        <v>3.988603988603988</v>
       </c>
       <c r="E7" s="3">
         <v>1.424501424501424</v>
@@ -11213,16 +11213,16 @@
         <v>0.8547008547008548</v>
       </c>
       <c r="G7" s="3">
-        <v>1.994301994301994</v>
+        <v>1.70940170940171</v>
       </c>
       <c r="H7" s="4">
-        <v>0.5666610415327152</v>
+        <v>0.5418825744252523</v>
       </c>
       <c r="I7" s="4">
-        <v>0.367855436107214</v>
+        <v>0.3420520175010591</v>
       </c>
       <c r="J7" s="4">
-        <v>0.7969263303969789</v>
+        <v>0.7800662606522161</v>
       </c>
       <c r="K7" s="4">
         <v>83.60340717483571</v>
@@ -11248,13 +11248,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="3">
-        <v>87.17948717948718</v>
+        <v>86.89458689458689</v>
       </c>
       <c r="C8" s="3">
         <v>10.82621082621083</v>
       </c>
       <c r="D8" s="3">
-        <v>1.994301994301994</v>
+        <v>2.279202279202279</v>
       </c>
       <c r="E8" s="3">
         <v>0.2849002849002849</v>
@@ -11263,16 +11263,16 @@
         <v>0.2849002849002849</v>
       </c>
       <c r="G8" s="3">
-        <v>1.424501424501424</v>
+        <v>1.70940170940171</v>
       </c>
       <c r="H8" s="4">
-        <v>0.5239654850497993</v>
+        <v>0.5146541349330473</v>
       </c>
       <c r="I8" s="4">
-        <v>0.371948216572372</v>
+        <v>0.3534387978448543</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8002834807703035</v>
+        <v>0.7926470881953966</v>
       </c>
       <c r="K8" s="4">
         <v>77.90036242417197</v>
@@ -11298,13 +11298,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="3">
-        <v>82.62108262108262</v>
+        <v>82.33618233618233</v>
       </c>
       <c r="C9" s="3">
         <v>13.96011396011396</v>
       </c>
       <c r="D9" s="3">
-        <v>3.418803418803419</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="E9" s="3">
         <v>1.13960113960114</v>
@@ -11313,16 +11313,16 @@
         <v>0.2849002849002849</v>
       </c>
       <c r="G9" s="3">
-        <v>1.994301994301994</v>
+        <v>2.279202279202279</v>
       </c>
       <c r="H9" s="4">
-        <v>0.5344675049383635</v>
+        <v>0.5290366866167272</v>
       </c>
       <c r="I9" s="4">
-        <v>0.3932814833666048</v>
+        <v>0.3783091366612667</v>
       </c>
       <c r="J9" s="4">
-        <v>0.5230548781968044</v>
+        <v>0.5234756605833694</v>
       </c>
       <c r="K9" s="4">
         <v>79.10072291024655</v>
@@ -11348,13 +11348,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="3">
-        <v>89.74358974358975</v>
+        <v>90.02849002849003</v>
       </c>
       <c r="C10" s="3">
         <v>7.977207977207977</v>
       </c>
       <c r="D10" s="3">
-        <v>2.279202279202279</v>
+        <v>1.994301994301994</v>
       </c>
       <c r="E10" s="3">
         <v>0.8547008547008548</v>
@@ -11363,16 +11363,16 @@
         <v>0.2849002849002849</v>
       </c>
       <c r="G10" s="3">
-        <v>1.13960113960114</v>
+        <v>0.8547008547008548</v>
       </c>
       <c r="H10" s="4">
-        <v>0.4489222911881933</v>
+        <v>0.4415715337789781</v>
       </c>
       <c r="I10" s="4">
-        <v>0.3840750531036541</v>
+        <v>0.3775147274902408</v>
       </c>
       <c r="J10" s="4">
-        <v>0.4443277163756275</v>
+        <v>0.4388737929795342</v>
       </c>
       <c r="K10" s="4">
         <v>83.0813807004276</v>
@@ -11398,13 +11398,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="3">
-        <v>82.33618233618233</v>
+        <v>82.62108262108262</v>
       </c>
       <c r="C11" s="3">
         <v>13.67521367521368</v>
       </c>
       <c r="D11" s="3">
-        <v>3.988603988603988</v>
+        <v>3.703703703703703</v>
       </c>
       <c r="E11" s="3">
         <v>2.279202279202279</v>
@@ -11413,16 +11413,16 @@
         <v>0.5698005698005698</v>
       </c>
       <c r="G11" s="3">
-        <v>1.13960113960114</v>
+        <v>0.8547008547008548</v>
       </c>
       <c r="H11" s="4">
-        <v>0.6418356013812807</v>
+        <v>0.6345920905793233</v>
       </c>
       <c r="I11" s="4">
-        <v>0.3346430751942596</v>
+        <v>0.3228648299612853</v>
       </c>
       <c r="J11" s="4">
-        <v>1.526418174417064</v>
+        <v>1.510886549022956</v>
       </c>
       <c r="K11" s="4">
         <v>74.23445161540393</v>
@@ -11448,13 +11448,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="3">
-        <v>88.03418803418803</v>
+        <v>88.31908831908832</v>
       </c>
       <c r="C12" s="3">
         <v>8.547008547008547</v>
       </c>
       <c r="D12" s="3">
-        <v>3.418803418803419</v>
+        <v>3.133903133903134</v>
       </c>
       <c r="E12" s="3">
         <v>1.424501424501424</v>
@@ -11463,16 +11463,16 @@
         <v>0.2849002849002849</v>
       </c>
       <c r="G12" s="3">
-        <v>1.70940170940171</v>
+        <v>1.424501424501424</v>
       </c>
       <c r="H12" s="4">
-        <v>0.7202316318488388</v>
+        <v>0.7067133002667413</v>
       </c>
       <c r="I12" s="4">
-        <v>0.3746790261179214</v>
+        <v>0.3622079836318077</v>
       </c>
       <c r="J12" s="4">
-        <v>0.8780974581767791</v>
+        <v>0.8625142472675008</v>
       </c>
       <c r="K12" s="4">
         <v>77.02754036087327</v>
@@ -11516,13 +11516,13 @@
         <v>1.13960113960114</v>
       </c>
       <c r="H13" s="4">
-        <v>0.5320325562766717</v>
+        <v>0.5226587111348853</v>
       </c>
       <c r="I13" s="4">
-        <v>0.3591139587081124</v>
+        <v>0.3453681268884816</v>
       </c>
       <c r="J13" s="4">
-        <v>1.175599641395253</v>
+        <v>1.162080025564664</v>
       </c>
       <c r="K13" s="4">
         <v>81.40085663895185</v>
@@ -11548,13 +11548,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="3">
-        <v>91.50943396226415</v>
+        <v>91.98113207547169</v>
       </c>
       <c r="C14" s="3">
         <v>5.660377358490567</v>
       </c>
       <c r="D14" s="3">
-        <v>2.830188679245283</v>
+        <v>2.358490566037736</v>
       </c>
       <c r="E14" s="3">
         <v>0.9433962264150944</v>
@@ -11563,16 +11563,16 @@
         <v>0.4716981132075472</v>
       </c>
       <c r="G14" s="3">
-        <v>1.415094339622642</v>
+        <v>0.9433962264150944</v>
       </c>
       <c r="H14" s="4">
-        <v>0.466243200694467</v>
+        <v>0.4360504610071106</v>
       </c>
       <c r="I14" s="4">
-        <v>0.4301662856536958</v>
+        <v>0.3992997197299444</v>
       </c>
       <c r="J14" s="4">
-        <v>0.4800775885358556</v>
+        <v>0.4508287845432251</v>
       </c>
       <c r="K14" s="4">
         <v>97.46967654986524</v>
@@ -11598,13 +11598,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="3">
-        <v>87.26415094339622</v>
+        <v>86.79245283018868</v>
       </c>
       <c r="C15" s="3">
         <v>11.32075471698113</v>
       </c>
       <c r="D15" s="3">
-        <v>1.415094339622642</v>
+        <v>1.886792452830189</v>
       </c>
       <c r="E15" s="3">
         <v>0.9433962264150944</v>
@@ -11613,16 +11613,16 @@
         <v>0.4716981132075472</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>0.4716981132075472</v>
       </c>
       <c r="H15" s="4">
-        <v>0.5121050460271698</v>
+        <v>0.5008769750257096</v>
       </c>
       <c r="I15" s="4">
-        <v>0.4644884844235578</v>
+        <v>0.4307607534295167</v>
       </c>
       <c r="J15" s="4">
-        <v>0.5271060156533525</v>
+        <v>0.501144847501947</v>
       </c>
       <c r="K15" s="4">
         <v>80.17295597484291</v>
@@ -11648,13 +11648,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="3">
-        <v>90.56603773584906</v>
+        <v>91.0377358490566</v>
       </c>
       <c r="C16" s="3">
         <v>6.60377358490566</v>
       </c>
       <c r="D16" s="3">
-        <v>2.830188679245283</v>
+        <v>2.358490566037736</v>
       </c>
       <c r="E16" s="3">
         <v>0.9433962264150944</v>
@@ -11663,16 +11663,16 @@
         <v>0.9433962264150944</v>
       </c>
       <c r="G16" s="3">
-        <v>0.9433962264150944</v>
+        <v>0.4716981132075472</v>
       </c>
       <c r="H16" s="4">
-        <v>0.4500766126619236</v>
+        <v>0.4288295348278384</v>
       </c>
       <c r="I16" s="4">
-        <v>0.4286180397145561</v>
+        <v>0.4062612271488339</v>
       </c>
       <c r="J16" s="4">
-        <v>0.4748747575434928</v>
+        <v>0.4505894612874244</v>
       </c>
       <c r="K16" s="4">
         <v>97.29736234116272</v>
@@ -11716,13 +11716,13 @@
         <v>1.415094339622642</v>
       </c>
       <c r="H17" s="4">
-        <v>0.6401820553313745</v>
+        <v>0.6114188940690597</v>
       </c>
       <c r="I17" s="4">
-        <v>0.5071549211664883</v>
+        <v>0.4550049238203273</v>
       </c>
       <c r="J17" s="4">
-        <v>0.8887935549769045</v>
+        <v>0.8578369457469368</v>
       </c>
       <c r="K17" s="4">
         <v>81.24839558464863</v>
@@ -12605,13 +12605,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C3" s="5">
         <v>32</v>
       </c>
       <c r="D3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" s="5">
         <v>8</v>
@@ -12620,7 +12620,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" s="5">
         <v>8</v>
@@ -12737,13 +12737,13 @@
         <v>20</v>
       </c>
       <c r="B6" s="5">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C6" s="5">
         <v>39</v>
       </c>
       <c r="D6" s="5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5">
         <v>6</v>
@@ -12752,7 +12752,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H6" s="5">
         <v>6</v>
@@ -12781,13 +12781,13 @@
         <v>21</v>
       </c>
       <c r="B7" s="5">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C7" s="5">
         <v>24</v>
       </c>
       <c r="D7" s="5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5">
         <v>5</v>
@@ -12796,7 +12796,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H7" s="5">
         <v>5</v>
@@ -12825,13 +12825,13 @@
         <v>22</v>
       </c>
       <c r="B8" s="5">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C8" s="5">
         <v>38</v>
       </c>
       <c r="D8" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="5">
         <v>1</v>
@@ -12840,7 +12840,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="5">
         <v>1</v>
@@ -12869,13 +12869,13 @@
         <v>23</v>
       </c>
       <c r="B9" s="5">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C9" s="5">
         <v>49</v>
       </c>
       <c r="D9" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5">
         <v>4</v>
@@ -12884,7 +12884,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H9" s="5">
         <v>4</v>
@@ -12913,13 +12913,13 @@
         <v>24</v>
       </c>
       <c r="B10" s="5">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" s="5">
         <v>28</v>
       </c>
       <c r="D10" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5">
         <v>3</v>
@@ -12928,7 +12928,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H10" s="5">
         <v>3</v>
@@ -12957,13 +12957,13 @@
         <v>25</v>
       </c>
       <c r="B11" s="5">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C11" s="5">
         <v>48</v>
       </c>
       <c r="D11" s="5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="5">
         <v>8</v>
@@ -12972,7 +12972,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H11" s="5">
         <v>8</v>
@@ -13001,13 +13001,13 @@
         <v>26</v>
       </c>
       <c r="B12" s="5">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C12" s="5">
         <v>30</v>
       </c>
       <c r="D12" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="5">
         <v>5</v>
@@ -13016,7 +13016,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="5">
         <v>5</v>
@@ -13089,13 +13089,13 @@
         <v>28</v>
       </c>
       <c r="B14" s="5">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C14" s="5">
         <v>12</v>
       </c>
       <c r="D14" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E14" s="5">
         <v>2</v>
@@ -13104,7 +13104,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" s="5">
         <v>2</v>
@@ -13133,13 +13133,13 @@
         <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C15" s="5">
         <v>24</v>
       </c>
       <c r="D15" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5">
         <v>2</v>
@@ -13148,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="5">
         <v>2</v>
@@ -13177,13 +13177,13 @@
         <v>30</v>
       </c>
       <c r="B16" s="5">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="5">
         <v>14</v>
       </c>
       <c r="D16" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5">
         <v>2</v>
@@ -13192,7 +13192,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" s="5">
         <v>2</v>
@@ -13419,16 +13419,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.810800794320867</v>
+        <v>-0.7784299194530604</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.5168351685531828</v>
+        <v>0.5127289623506104</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4212739909423495</v>
+        <v>0.4187829086635048</v>
       </c>
       <c r="R3" s="5">
         <v>35</v>
@@ -13478,16 +13478,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9656041787261096</v>
+        <v>-0.9925406319543413</v>
       </c>
       <c r="O4" s="5">
         <v>21</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6207388446722005</v>
+        <v>0.6177459054246192</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3927838178927447</v>
+        <v>0.3915011296437813</v>
       </c>
       <c r="R4" s="5">
         <v>21</v>
@@ -13537,22 +13537,22 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2071483744769189</v>
+        <v>-0.02749425638609893</v>
       </c>
       <c r="O5" s="5">
         <v>20</v>
       </c>
       <c r="P5" s="4">
-        <v>2.465347673037289</v>
+        <v>2.45317749072772</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6561780957681439</v>
+        <v>0.6838062394873056</v>
       </c>
       <c r="R5" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -13596,16 +13596,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.8901307188714881</v>
+        <v>-1.130471309844978</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.9123387538138262</v>
+        <v>0.9353407898955531</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.674967954628425</v>
+        <v>0.6522145054697807</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -13655,13 +13655,13 @@
         <v>2</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.445796896480792</v>
+        <v>-1.529535730039655</v>
       </c>
       <c r="O7" s="5">
         <v>14</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5744874790666838</v>
+        <v>0.564020124871826</v>
       </c>
       <c r="Q7" s="4">
         <v>0.555380252253067</v>
@@ -13714,16 +13714,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.790324446784666</v>
+        <v>-1.687630299631337</v>
       </c>
       <c r="O8" s="5">
         <v>8</v>
       </c>
       <c r="P8" s="4">
-        <v>0.571451606184084</v>
+        <v>0.5958374008496131</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4016847350891055</v>
+        <v>0.3869163535107347</v>
       </c>
       <c r="R8" s="5">
         <v>8</v>
@@ -13773,16 +13773,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.6293632817857671</v>
+        <v>-0.5801696045464979</v>
       </c>
       <c r="O9" s="5">
         <v>10</v>
       </c>
       <c r="P9" s="4">
-        <v>1.106656342349611</v>
+        <v>1.095307821131183</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3106366603677747</v>
+        <v>0.3068571703535142</v>
       </c>
       <c r="R9" s="5">
         <v>10</v>
@@ -13832,16 +13832,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1236712158267778</v>
+        <v>-0.1640072412505731</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2514292890188761</v>
+        <v>0.2373497039306685</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1059137528785089</v>
+        <v>0.09708545585741887</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -13891,16 +13891,16 @@
         <v>1</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.7549033517086159</v>
+        <v>-0.7187706703350898</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>0.8311814282052336</v>
+        <v>0.8208732020137516</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3660288954216731</v>
+        <v>0.3608855602665997</v>
       </c>
       <c r="R11" s="5">
         <v>10</v>
@@ -14007,16 +14007,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.1312645190664</v>
+        <v>0.07540152986328508</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.5688206494107135</v>
+        <v>0.5983443706863828</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6785752416999957</v>
+        <v>0.6372420319140588</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -14066,16 +14066,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.748367746798702</v>
+        <v>-1.582021983400267</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4028333214843687</v>
+        <v>0.3661305545703044</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.4028333214843687</v>
+        <v>0.3661305545703044</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -14182,16 +14182,16 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>-1.45309337569592</v>
+        <v>-1.296120383438108</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
       </c>
       <c r="P16" s="4">
-        <v>3.646163987403639</v>
+        <v>3.55474882876301</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.3595161588937436</v>
+        <v>0.2812125669765521</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -14364,16 +14364,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.8208854903454168</v>
+        <v>-0.7295665058984184</v>
       </c>
       <c r="O3" s="5">
         <v>33</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4467541167129754</v>
+        <v>0.4405636719256146</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4402517716923715</v>
+        <v>0.4277764860552095</v>
       </c>
       <c r="R3" s="5">
         <v>33</v>
@@ -14423,16 +14423,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.9203371534632699</v>
+        <v>-1.043346840507809</v>
       </c>
       <c r="O4" s="5">
         <v>18</v>
       </c>
       <c r="P4" s="4">
-        <v>0.6047759358511351</v>
+        <v>0.5612432603558091</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3058254206374461</v>
+        <v>0.2851050960554949</v>
       </c>
       <c r="R4" s="5">
         <v>18</v>
@@ -14482,16 +14482,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.03625313693275577</v>
+        <v>0.1743589970312769</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>0.6839607783985305</v>
+        <v>0.6755165044032154</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6768153140211471</v>
+        <v>0.6428840601834258</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -14541,16 +14541,16 @@
         <v>2</v>
       </c>
       <c r="N6" s="4">
-        <v>-1.191570178638721</v>
+        <v>-1.409522905683588</v>
       </c>
       <c r="O6" s="5">
         <v>19</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7305560348345811</v>
+        <v>0.7397885832201103</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5918332219338417</v>
+        <v>0.5571246800753</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -14600,16 +14600,16 @@
         <v>4</v>
       </c>
       <c r="N7" s="4">
-        <v>-1.908867224325077</v>
+        <v>-1.981177792890605</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5586870179394166</v>
+        <v>0.5406093757980344</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5356829483182649</v>
+        <v>0.5276484406998728</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -14716,13 +14716,13 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.218482213142579</v>
+        <v>-0.1994470131640753</v>
       </c>
       <c r="O9" s="5">
         <v>10</v>
       </c>
       <c r="P9" s="4">
-        <v>0.2965418138346401</v>
+        <v>0.2980010811360702</v>
       </c>
       <c r="Q9" s="4">
         <v>0.3398401494160225</v>
@@ -14775,16 +14775,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.1486772492838497</v>
+        <v>-0.1142805219531056</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3534911973763002</v>
+        <v>0.3572515308789074</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1439236453645789</v>
+        <v>0.1374718475911405</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -14834,7 +14834,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>0.1269605695112107</v>
+        <v>0.1245225829101599</v>
       </c>
       <c r="O11" s="5">
         <v>12</v>
@@ -14950,16 +14950,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>-0.57472683877441</v>
+        <v>-0.7562939671093716</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.4390599146686652</v>
+        <v>0.4131217534779564</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.3911056013769553</v>
+        <v>0.354792175709963</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -15009,16 +15009,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.674307068316646</v>
+        <v>-1.48515267642577</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4559795987292496</v>
+        <v>0.4051424925573788</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.4559795987292496</v>
+        <v>0.4051424925573788</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -15068,7 +15068,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.914951134104976</v>
+        <v>-0.8246974487231569</v>
       </c>
       <c r="O15" s="5">
         <v>5</v>
@@ -15077,7 +15077,7 @@
         <v>0.4431214171822049</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.2167085615568328</v>
+        <v>0.198657824480469</v>
       </c>
       <c r="R15" s="5">
         <v>5</v>
@@ -15127,7 +15127,7 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>-1.217635506249513</v>
+        <v>-0.9567970019531344</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
@@ -15136,7 +15136,7 @@
         <v>0.604210193509104</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.7248471714271386</v>
+        <v>0.6726794705678628</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -15309,16 +15309,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.482627090541767</v>
+        <v>-0.3464897741148931</v>
       </c>
       <c r="O3" s="5">
         <v>34</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4630813016540233</v>
+        <v>0.4494422282080915</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.468631153425383</v>
+        <v>0.4497845936040196</v>
       </c>
       <c r="R3" s="5">
         <v>34</v>
@@ -15368,16 +15368,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3130325907008763</v>
+        <v>-0.3030505683449576</v>
       </c>
       <c r="O4" s="5">
         <v>19</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5472771138091022</v>
+        <v>0.5469074092774014</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3108753863602908</v>
+        <v>0.3103500167626108</v>
       </c>
       <c r="R4" s="5">
         <v>19</v>
@@ -15427,16 +15427,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.362315085981596</v>
+        <v>-0.2262542147511795</v>
       </c>
       <c r="O5" s="5">
         <v>23</v>
       </c>
       <c r="P5" s="4">
-        <v>0.7568080608428809</v>
+        <v>0.7560937645833006</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7652418288257871</v>
+        <v>0.7407405469157725</v>
       </c>
       <c r="R5" s="5">
         <v>23</v>
@@ -15486,16 +15486,16 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.3195322127509033</v>
+        <v>-0.6242145551047713</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>0.6567097099199541</v>
+        <v>0.6874355420007753</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.5160871278639587</v>
+        <v>0.470713929313378</v>
       </c>
       <c r="R6" s="5">
         <v>18</v>
@@ -15545,7 +15545,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.595681501613146</v>
+        <v>-0.5930562885412485</v>
       </c>
       <c r="O7" s="5">
         <v>9</v>
@@ -15554,7 +15554,7 @@
         <v>0.5834697416137971</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.4657608117824046</v>
+        <v>0.4654691214410825</v>
       </c>
       <c r="R7" s="5">
         <v>9</v>
@@ -15604,16 +15604,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.8251106685081424</v>
+        <v>-0.6534869726489347</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>0.5064065214022472</v>
+        <v>0.4968364362435527</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3674803256309462</v>
+        <v>0.3216714842686713</v>
       </c>
       <c r="R8" s="5">
         <v>10</v>
@@ -15663,16 +15663,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.1177336658391306</v>
+        <v>-0.2343113353913395</v>
       </c>
       <c r="O9" s="5">
         <v>11</v>
       </c>
       <c r="P9" s="4">
-        <v>0.4253883063691142</v>
+        <v>0.3967577071643653</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.4425783122858409</v>
+        <v>0.4219429012944974</v>
       </c>
       <c r="R9" s="5">
         <v>11</v>
@@ -15722,16 +15722,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.0603837419723858</v>
+        <v>-0.1077266247353066</v>
       </c>
       <c r="O10" s="5">
         <v>9</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3306548161767475</v>
+        <v>0.3130017076496306</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1133808198825353</v>
+        <v>0.1056243027673531</v>
       </c>
       <c r="R10" s="5">
         <v>9</v>
@@ -15781,16 +15781,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.1577704499013932</v>
+        <v>-0.1848684994926515</v>
       </c>
       <c r="O11" s="5">
         <v>11</v>
       </c>
       <c r="P11" s="4">
-        <v>0.528150640360234</v>
+        <v>0.5265501346124223</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3895780767165432</v>
+        <v>0.3853686113924523</v>
       </c>
       <c r="R11" s="5">
         <v>11</v>
@@ -15897,16 +15897,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.7467600591824445</v>
+        <v>0.6658942648551545</v>
       </c>
       <c r="O13" s="5">
         <v>6</v>
       </c>
       <c r="P13" s="4">
-        <v>0.6320145357950773</v>
+        <v>0.6001720399451317</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6512831361630195</v>
+        <v>0.627611190059298</v>
       </c>
       <c r="R13" s="5">
         <v>6</v>
@@ -15956,16 +15956,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.8869753381893114</v>
+        <v>-0.6845412012242349</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.4131095937574274</v>
+        <v>0.3355296665001883</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.4131095937574274</v>
+        <v>0.3355296665001883</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.2988474194004624</v>
+        <v>-0.3680759405859391</v>
       </c>
       <c r="O15" s="5">
         <v>5</v>
       </c>
       <c r="P15" s="4">
-        <v>0.3271621684154273</v>
+        <v>0.2857041027580109</v>
       </c>
       <c r="Q15" s="4">
-        <v>0.1392991894351678</v>
+        <v>0.1033952148833635</v>
       </c>
       <c r="R15" s="5">
         <v>5</v>
@@ -16074,7 +16074,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.657736173130121</v>
+        <v>-0.368787705310524</v>
       </c>
       <c r="O16" s="5">
         <v>5</v>
@@ -16083,7 +16083,7 @@
         <v>0.4773551156662326</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.5663358451141198</v>
+        <v>0.5085461515502004</v>
       </c>
       <c r="R16" s="5">
         <v>5</v>
@@ -16256,13 +16256,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3490821673391407</v>
+        <v>-0.3469602964111402</v>
       </c>
       <c r="O3" s="5">
         <v>35</v>
       </c>
       <c r="P3" s="4">
-        <v>0.524092272104372</v>
+        <v>0.5240349242414531</v>
       </c>
       <c r="Q3" s="4">
         <v>0.4940517697374811</v>
@@ -16315,16 +16315,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.3632337421020502</v>
+        <v>-0.5333828114806991</v>
       </c>
       <c r="O4" s="5">
         <v>16</v>
       </c>
       <c r="P4" s="4">
-        <v>0.5517898710921663</v>
+        <v>0.5356090406890196</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.3880828647572332</v>
+        <v>0.3619928944689974</v>
       </c>
       <c r="R4" s="5">
         <v>16</v>
@@ -16374,16 +16374,16 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2277719654961479</v>
+        <v>-0.1720903386248835</v>
       </c>
       <c r="O5" s="5">
         <v>21</v>
       </c>
       <c r="P5" s="4">
-        <v>0.8113197062105226</v>
+        <v>0.8076918266218153</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6624631801727118</v>
+        <v>0.6492132986972671</v>
       </c>
       <c r="R5" s="5">
         <v>20</v>
@@ -16433,22 +16433,22 @@
         <v>0</v>
       </c>
       <c r="N6" s="4">
-        <v>-0.1297791387555584</v>
+        <v>-0.3331745863586519</v>
       </c>
       <c r="O6" s="5">
         <v>18</v>
       </c>
       <c r="P6" s="4">
-        <v>0.7916890441488841</v>
+        <v>0.8165394000925634</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.6255417621181798</v>
+        <v>0.5114070356548694</v>
       </c>
       <c r="R6" s="5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S6" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="25" customHeight="1">
@@ -16492,22 +16492,22 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <v>-0.7233417566827356</v>
+        <v>-1.021809647366325</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.611624051511221</v>
+        <v>0.5239730831689435</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.6409041098046799</v>
+        <v>0.4498899149591631</v>
       </c>
       <c r="R7" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="25" customHeight="1">
@@ -16551,16 +16551,16 @@
         <v>1</v>
       </c>
       <c r="N8" s="4">
-        <v>-1.043605890330282</v>
+        <v>-0.7976450558911097</v>
       </c>
       <c r="O8" s="5">
         <v>7</v>
       </c>
       <c r="P8" s="4">
-        <v>0.6345762108038103</v>
+        <v>0.7165631556168677</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.4476423594036932</v>
+        <v>0.4125050973409543</v>
       </c>
       <c r="R8" s="5">
         <v>7</v>
@@ -16610,16 +16610,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.4413649869012488</v>
+        <v>-0.3928599712481855</v>
       </c>
       <c r="O9" s="5">
         <v>8</v>
       </c>
       <c r="P9" s="4">
-        <v>0.5781179637827556</v>
+        <v>0.5590752830981541</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.3610823145855662</v>
+        <v>0.3446445474719297</v>
       </c>
       <c r="R9" s="5">
         <v>8</v>
@@ -16669,16 +16669,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.284264441350705</v>
+        <v>-0.2163615810284512</v>
       </c>
       <c r="O10" s="5">
         <v>12</v>
       </c>
       <c r="P10" s="4">
-        <v>0.2259995815299515</v>
+        <v>0.2107624103157638</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.2259995815299515</v>
+        <v>0.2107624103157638</v>
       </c>
       <c r="R10" s="5">
         <v>12</v>
@@ -16728,16 +16728,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.3966229790889869</v>
+        <v>-0.2916058340997267</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>0.6268425868051754</v>
+        <v>0.5904607967334018</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3428981676996108</v>
+        <v>0.3202434486113347</v>
       </c>
       <c r="R11" s="5">
         <v>10</v>
@@ -16844,16 +16844,16 @@
         <v>0</v>
       </c>
       <c r="N13" s="4">
-        <v>0.8320525890878969</v>
+        <v>0.9016916604785195</v>
       </c>
       <c r="O13" s="5">
         <v>5</v>
       </c>
       <c r="P13" s="4">
-        <v>0.5477181801026777</v>
+        <v>0.5576666188727667</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6844004370124959</v>
+        <v>0.6704726227343712</v>
       </c>
       <c r="R13" s="5">
         <v>5</v>
@@ -16903,16 +16903,16 @@
         <v>1</v>
       </c>
       <c r="N14" s="4">
-        <v>-1.264223218091833</v>
+        <v>-1.132891065097027</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3425225017816855</v>
+        <v>0.2998058412044221</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3425225017816855</v>
+        <v>0.2998058412044221</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -16962,7 +16962,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="4">
-        <v>-0.344415222488396</v>
+        <v>-0.3049957549981599</v>
       </c>
       <c r="O15" s="5">
         <v>6</v>
@@ -17021,16 +17021,16 @@
         <v>1</v>
       </c>
       <c r="N16" s="4">
-        <v>-1.018492193331501</v>
+        <v>-0.8250339469512937</v>
       </c>
       <c r="O16" s="5">
         <v>6</v>
       </c>
       <c r="P16" s="4">
-        <v>0.4569634329600629</v>
+        <v>0.4516045009635311</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4569634329600629</v>
+        <v>0.4516045009635311</v>
       </c>
       <c r="R16" s="5">
         <v>6</v>
@@ -17203,16 +17203,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1521105512575909</v>
+        <v>-0.1734017412182567</v>
       </c>
       <c r="O3" s="5">
         <v>36</v>
       </c>
       <c r="P3" s="4">
-        <v>0.4331224723129264</v>
+        <v>0.4331922676080138</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4326634976204259</v>
+        <v>0.4321438097303584</v>
       </c>
       <c r="R3" s="5">
         <v>36</v>
@@ -17262,16 +17262,16 @@
         <v>1</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06913760468898629</v>
+        <v>-0.3057555674780303</v>
       </c>
       <c r="O4" s="5">
         <v>23</v>
       </c>
       <c r="P4" s="4">
-        <v>0.7243170459186985</v>
+        <v>0.6746009478167444</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.4485082994118086</v>
+        <v>0.3982484500498215</v>
       </c>
       <c r="R4" s="5">
         <v>22</v>
@@ -17321,22 +17321,22 @@
         <v>1</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3062037934057713</v>
+        <v>-0.1047594680102435</v>
       </c>
       <c r="O5" s="5">
         <v>24</v>
       </c>
       <c r="P5" s="4">
-        <v>1.523688484823491</v>
+        <v>1.346429251620005</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.7984346183860047</v>
+        <v>0.6480672876082683</v>
       </c>
       <c r="R5" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="S5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="25" customHeight="1">
@@ -17380,16 +17380,16 @@
         <v>1</v>
       </c>
       <c r="N6" s="4">
-        <v>0.3597597768015163</v>
+        <v>-0.09285041998536769</v>
       </c>
       <c r="O6" s="5">
         <v>20</v>
       </c>
       <c r="P6" s="4">
-        <v>0.8536093600929368</v>
+        <v>0.8424907030850928</v>
       </c>
       <c r="Q6" s="4">
-        <v>0.7102566731811946</v>
+        <v>0.6119584599812414</v>
       </c>
       <c r="R6" s="5">
         <v>19</v>
@@ -17439,16 +17439,16 @@
         <v>1</v>
       </c>
       <c r="N7" s="4">
-        <v>0.1973311821419325</v>
+        <v>0.01529490897705443</v>
       </c>
       <c r="O7" s="5">
         <v>12</v>
       </c>
       <c r="P7" s="4">
-        <v>0.5929662737386027</v>
+        <v>0.561889868796996</v>
       </c>
       <c r="Q7" s="4">
-        <v>0.5087458775770117</v>
+        <v>0.4598793860782112</v>
       </c>
       <c r="R7" s="5">
         <v>11</v>
@@ -17498,16 +17498,16 @@
         <v>0</v>
       </c>
       <c r="N8" s="4">
-        <v>-0.61097908970508</v>
+        <v>-0.5472082179101676</v>
       </c>
       <c r="O8" s="5">
         <v>10</v>
       </c>
       <c r="P8" s="4">
-        <v>0.4817054103835895</v>
+        <v>0.4751004955926561</v>
       </c>
       <c r="Q8" s="4">
-        <v>0.3403968288815452</v>
+        <v>0.3197167567734425</v>
       </c>
       <c r="R8" s="5">
         <v>10</v>
@@ -17557,16 +17557,16 @@
         <v>0</v>
       </c>
       <c r="N9" s="4">
-        <v>-0.1489658189409184</v>
+        <v>-0.1013914806909071</v>
       </c>
       <c r="O9" s="5">
         <v>10</v>
       </c>
       <c r="P9" s="4">
-        <v>1.371850440504315</v>
+        <v>1.36091838990926</v>
       </c>
       <c r="Q9" s="4">
-        <v>0.2976060359781263</v>
+        <v>0.2940024429140621</v>
       </c>
       <c r="R9" s="5">
         <v>10</v>
@@ -17616,16 +17616,16 @@
         <v>0</v>
       </c>
       <c r="N10" s="4">
-        <v>-0.008436134816889762</v>
+        <v>-0.08907225856689394</v>
       </c>
       <c r="O10" s="5">
         <v>10</v>
       </c>
       <c r="P10" s="4">
-        <v>0.3187024538378888</v>
+        <v>0.2846311305045515</v>
       </c>
       <c r="Q10" s="4">
-        <v>0.1433697340585894</v>
+        <v>0.1186113708085856</v>
       </c>
       <c r="R10" s="5">
         <v>10</v>
@@ -17675,16 +17675,16 @@
         <v>0</v>
       </c>
       <c r="N11" s="4">
-        <v>-0.260342871590818</v>
+        <v>-0.2309140099487053</v>
       </c>
       <c r="O11" s="5">
         <v>10</v>
       </c>
       <c r="P11" s="4">
-        <v>1.30115279582625</v>
+        <v>1.296247985552565</v>
       </c>
       <c r="Q11" s="4">
-        <v>0.3217769157172838</v>
+        <v>0.3217769157172839</v>
       </c>
       <c r="R11" s="5">
         <v>10</v>
@@ -17734,16 +17734,16 @@
         <v>0</v>
       </c>
       <c r="N12" s="4">
-        <v>0.4323372440825324</v>
+        <v>0.4138547448754935</v>
       </c>
       <c r="O12" s="5">
         <v>5</v>
       </c>
       <c r="P12" s="4">
-        <v>0.5139720214695053</v>
+        <v>0.5119184104465009</v>
       </c>
       <c r="Q12" s="4">
-        <v>0.350054451181245</v>
+        <v>0.3463579513398372</v>
       </c>
       <c r="R12" s="5">
         <v>5</v>
@@ -17793,16 +17793,16 @@
         <v>2</v>
       </c>
       <c r="N13" s="4">
-        <v>1.380196378911137</v>
+        <v>1.268372128286131</v>
       </c>
       <c r="O13" s="5">
         <v>6</v>
       </c>
       <c r="P13" s="4">
-        <v>0.581179825750557</v>
+        <v>0.5359520627706453</v>
       </c>
       <c r="Q13" s="4">
-        <v>0.6273740061328112</v>
+        <v>0.5932456577604152</v>
       </c>
       <c r="R13" s="5">
         <v>6</v>
@@ -17852,16 +17852,16 @@
         <v>0</v>
       </c>
       <c r="N14" s="4">
-        <v>-0.7872883877441362</v>
+        <v>-0.6103261736230365</v>
       </c>
       <c r="O14" s="5">
         <v>6</v>
       </c>
       <c r="P14" s="4">
-        <v>0.3937013280078139</v>
+        <v>0.3023557474609409</v>
       </c>
       <c r="Q14" s="4">
-        <v>0.3937013280078139</v>
+        <v>0.3023557474609409</v>
       </c>
       <c r="R14" s="5">
         <v>6</v>
@@ -17968,16 +17968,16 @@
         <v>0</v>
       </c>
       <c r="N16" s="4">
-        <v>-0.4352420680822746</v>
+        <v>-0.3343278057897976</v>
       </c>
       <c r="O16" s="5">
         <v>6</v>
       </c>
       <c r="P16" s="4">
-        <v>0.4204462273136376</v>
+        <v>0.3881218695186372</v>
       </c>
       <c r="Q16" s="4">
-        <v>0.4204462273136376</v>
+        <v>0.3881218695186372</v>
       </c>
       <c r="R16" s="5">
         <v>6</v>
